--- a/Employee_Reports_wi48/Renato Dimalanta Canlas Q0274.xlsx
+++ b/Employee_Reports_wi48/Renato Dimalanta Canlas Q0274.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1362,11 +1362,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1411,11 +1411,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1460,11 +1460,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1483,9 +1483,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
           <t>25-Mar-2025</t>
@@ -1497,11 +1509,11 @@
         </is>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-110</v>
+        <v>-113</v>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -1520,9 +1532,21 @@
           <t>Equipment Operation Procedure(QDF-SOP-003) (SOPs)</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>DFWH</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>LSME-QDF-SOP-003</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
           <t>04-May-2026</t>
@@ -1534,11 +1558,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1583,11 +1607,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1632,11 +1656,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1669,11 +1693,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1706,11 +1730,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
